--- a/base_dados.xlsx
+++ b/base_dados.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SistemaInspecao\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maico\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DDA15D9-2C9C-4E34-B0DB-23271A396577}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6099B67F-29F1-48E5-8D0C-F2F3BD6BFD42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Equipamentos" sheetId="1" r:id="rId1"/>
@@ -6069,13 +6069,13 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
-        <v>46110</v>
+        <v>46126</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>140</v>
       </c>
       <c r="C2" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>93</v>
@@ -6083,13 +6083,13 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
-        <v>46110</v>
+        <v>46126</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>152</v>
       </c>
       <c r="C3" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>93</v>
@@ -6097,13 +6097,13 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
-        <v>46110</v>
+        <v>46126</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>103</v>
       </c>
       <c r="C4" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>93</v>
@@ -6111,13 +6111,13 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
-        <v>46110</v>
+        <v>46126</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>90</v>
       </c>
       <c r="C5" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D5" s="12" t="s">
         <v>93</v>
@@ -6125,13 +6125,13 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
-        <v>46110</v>
+        <v>46126</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>111</v>
       </c>
       <c r="C6" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D6" s="12" t="s">
         <v>93</v>
@@ -6139,13 +6139,13 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
-        <v>46110</v>
+        <v>46126</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>179</v>
       </c>
       <c r="C7" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D7" s="12" t="s">
         <v>93</v>
@@ -6153,13 +6153,13 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
-        <v>46110</v>
+        <v>46126</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>116</v>
       </c>
       <c r="C8" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" s="12" t="s">
         <v>93</v>
@@ -6167,13 +6167,13 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
-        <v>46110</v>
+        <v>46126</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>121</v>
       </c>
       <c r="C9" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9" s="12" t="s">
         <v>93</v>
@@ -6181,13 +6181,13 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
-        <v>46110</v>
+        <v>46126</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>126</v>
       </c>
       <c r="C10" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" s="12" t="s">
         <v>93</v>
@@ -6195,13 +6195,13 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
-        <v>46110</v>
+        <v>46126</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>189</v>
       </c>
       <c r="C11" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11" s="12" t="s">
         <v>93</v>
@@ -6209,13 +6209,13 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
-        <v>46110</v>
+        <v>46126</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>203</v>
       </c>
       <c r="C12" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" s="12" t="s">
         <v>93</v>
@@ -6223,7 +6223,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
-        <v>46110</v>
+        <v>46126</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>138</v>
@@ -6237,7 +6237,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
-        <v>46110</v>
+        <v>46126</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>185</v>
@@ -6251,7 +6251,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
-        <v>46110</v>
+        <v>46126</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>129</v>
@@ -6265,7 +6265,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
-        <v>46110</v>
+        <v>46126</v>
       </c>
       <c r="B16" t="s">
         <v>9</v>
@@ -6279,7 +6279,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
-        <v>46110</v>
+        <v>46126</v>
       </c>
       <c r="B17" t="s">
         <v>15</v>
@@ -6293,7 +6293,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
-        <v>46110</v>
+        <v>46126</v>
       </c>
       <c r="B18" t="s">
         <v>16</v>
@@ -6307,7 +6307,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
-        <v>46110</v>
+        <v>46126</v>
       </c>
       <c r="B19" t="s">
         <v>17</v>
@@ -6321,7 +6321,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
-        <v>46110</v>
+        <v>46126</v>
       </c>
       <c r="B20" t="s">
         <v>18</v>
@@ -6335,7 +6335,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
-        <v>46110</v>
+        <v>46126</v>
       </c>
       <c r="B21" t="s">
         <v>19</v>
@@ -6349,7 +6349,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
-        <v>46110</v>
+        <v>46126</v>
       </c>
       <c r="B22" t="s">
         <v>20</v>
@@ -6363,7 +6363,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
-        <v>46110</v>
+        <v>46126</v>
       </c>
       <c r="B23" t="s">
         <v>21</v>
@@ -6377,7 +6377,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
-        <v>46110</v>
+        <v>46126</v>
       </c>
       <c r="B24" t="s">
         <v>9</v>
@@ -6391,7 +6391,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
-        <v>46110</v>
+        <v>46126</v>
       </c>
       <c r="B25" t="s">
         <v>15</v>
@@ -6405,7 +6405,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
-        <v>46110</v>
+        <v>46126</v>
       </c>
       <c r="B26" t="s">
         <v>16</v>
@@ -6419,7 +6419,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
-        <v>46110</v>
+        <v>46126</v>
       </c>
       <c r="B27" t="s">
         <v>17</v>
@@ -6433,7 +6433,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
-        <v>46110</v>
+        <v>46126</v>
       </c>
       <c r="B28" t="s">
         <v>18</v>
@@ -6447,7 +6447,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
-        <v>46110</v>
+        <v>46126</v>
       </c>
       <c r="B29" t="s">
         <v>19</v>
@@ -6461,7 +6461,7 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
-        <v>46110</v>
+        <v>46126</v>
       </c>
       <c r="B30" t="s">
         <v>20</v>
@@ -6475,7 +6475,7 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
-        <v>46110</v>
+        <v>46126</v>
       </c>
       <c r="B31" t="s">
         <v>21</v>
@@ -6489,7 +6489,7 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
-        <v>46111</v>
+        <v>46127</v>
       </c>
       <c r="B32" t="s">
         <v>9</v>
@@ -6503,7 +6503,7 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
-        <v>46111</v>
+        <v>46127</v>
       </c>
       <c r="B33" t="s">
         <v>15</v>
@@ -6517,7 +6517,7 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
-        <v>46111</v>
+        <v>46127</v>
       </c>
       <c r="B34" t="s">
         <v>16</v>
@@ -6531,7 +6531,7 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
-        <v>46111</v>
+        <v>46127</v>
       </c>
       <c r="B35" t="s">
         <v>17</v>
@@ -6545,7 +6545,7 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
-        <v>46111</v>
+        <v>46127</v>
       </c>
       <c r="B36" t="s">
         <v>18</v>
@@ -6559,7 +6559,7 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
-        <v>46111</v>
+        <v>46127</v>
       </c>
       <c r="B37" t="s">
         <v>19</v>
@@ -6573,7 +6573,7 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
-        <v>46111</v>
+        <v>46127</v>
       </c>
       <c r="B38" t="s">
         <v>20</v>
@@ -6587,7 +6587,7 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
-        <v>46111</v>
+        <v>46127</v>
       </c>
       <c r="B39" t="s">
         <v>21</v>
@@ -6601,7 +6601,7 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
-        <v>46111</v>
+        <v>46127</v>
       </c>
       <c r="B40" t="s">
         <v>9</v>
@@ -6615,7 +6615,7 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
-        <v>46111</v>
+        <v>46127</v>
       </c>
       <c r="B41" t="s">
         <v>15</v>
@@ -6629,7 +6629,7 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="5">
-        <v>46111</v>
+        <v>46127</v>
       </c>
       <c r="B42" t="s">
         <v>16</v>
@@ -6643,7 +6643,7 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
-        <v>46111</v>
+        <v>46127</v>
       </c>
       <c r="B43" t="s">
         <v>17</v>
@@ -6657,7 +6657,7 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="5">
-        <v>46111</v>
+        <v>46127</v>
       </c>
       <c r="B44" t="s">
         <v>18</v>
@@ -6671,7 +6671,7 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="5">
-        <v>46111</v>
+        <v>46127</v>
       </c>
       <c r="B45" t="s">
         <v>19</v>
@@ -6685,7 +6685,7 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="5">
-        <v>46111</v>
+        <v>46127</v>
       </c>
       <c r="B46" t="s">
         <v>20</v>
@@ -6699,7 +6699,7 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="5">
-        <v>46111</v>
+        <v>46127</v>
       </c>
       <c r="B47" t="s">
         <v>21</v>
@@ -6713,7 +6713,7 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="5">
-        <v>46111</v>
+        <v>46127</v>
       </c>
       <c r="B48" t="s">
         <v>9</v>
@@ -6727,7 +6727,7 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="5">
-        <v>46111</v>
+        <v>46127</v>
       </c>
       <c r="B49" t="s">
         <v>15</v>
@@ -6741,7 +6741,7 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="5">
-        <v>46111</v>
+        <v>46127</v>
       </c>
       <c r="B50" t="s">
         <v>16</v>
@@ -6755,7 +6755,7 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="5">
-        <v>46111</v>
+        <v>46127</v>
       </c>
       <c r="B51" t="s">
         <v>17</v>
@@ -6769,7 +6769,7 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="5">
-        <v>46111</v>
+        <v>46127</v>
       </c>
       <c r="B52" t="s">
         <v>18</v>
@@ -6783,7 +6783,7 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="5">
-        <v>46111</v>
+        <v>46127</v>
       </c>
       <c r="B53" t="s">
         <v>19</v>
@@ -6797,7 +6797,7 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="5">
-        <v>46111</v>
+        <v>46127</v>
       </c>
       <c r="B54" t="s">
         <v>20</v>
@@ -6811,7 +6811,7 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="5">
-        <v>46111</v>
+        <v>46127</v>
       </c>
       <c r="B55" t="s">
         <v>21</v>
@@ -6825,7 +6825,7 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="5">
-        <v>46111</v>
+        <v>46127</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>22</v>
@@ -6839,7 +6839,7 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="5">
-        <v>46111</v>
+        <v>46127</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>22</v>
@@ -6853,7 +6853,7 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="5">
-        <v>46111</v>
+        <v>46127</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>22</v>
@@ -6867,7 +6867,7 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="5">
-        <v>46111</v>
+        <v>46127</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>56</v>
@@ -6881,7 +6881,7 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="5">
-        <v>46111</v>
+        <v>46127</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>56</v>
@@ -6895,7 +6895,7 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="5">
-        <v>46111</v>
+        <v>46127</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>56</v>
@@ -6909,7 +6909,7 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="5">
-        <v>46111</v>
+        <v>46127</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>60</v>
@@ -6923,7 +6923,7 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="5">
-        <v>46111</v>
+        <v>46127</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>60</v>
@@ -6937,7 +6937,7 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="5">
-        <v>46111</v>
+        <v>46127</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>60</v>
@@ -6951,7 +6951,7 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="5">
-        <v>46111</v>
+        <v>46127</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>68</v>
@@ -6965,7 +6965,7 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="5">
-        <v>46111</v>
+        <v>46127</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>68</v>
@@ -6979,7 +6979,7 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="5">
-        <v>46111</v>
+        <v>46127</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>68</v>
@@ -6993,7 +6993,7 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="5">
-        <v>46111</v>
+        <v>46127</v>
       </c>
       <c r="B68" s="14" t="s">
         <v>72</v>
@@ -7007,7 +7007,7 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="5">
-        <v>46111</v>
+        <v>46127</v>
       </c>
       <c r="B69" s="14" t="s">
         <v>72</v>
@@ -7021,7 +7021,7 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="5">
-        <v>46111</v>
+        <v>46127</v>
       </c>
       <c r="B70" s="14" t="s">
         <v>72</v>
@@ -7035,7 +7035,7 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="5">
-        <v>46112</v>
+        <v>46128</v>
       </c>
       <c r="B71" t="s">
         <v>9</v>
@@ -7049,7 +7049,7 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="5">
-        <v>46112</v>
+        <v>46128</v>
       </c>
       <c r="B72" t="s">
         <v>15</v>
@@ -7063,7 +7063,7 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="5">
-        <v>46112</v>
+        <v>46128</v>
       </c>
       <c r="B73" t="s">
         <v>16</v>
@@ -7077,7 +7077,7 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="5">
-        <v>46112</v>
+        <v>46128</v>
       </c>
       <c r="B74" t="s">
         <v>17</v>
@@ -7091,7 +7091,7 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="5">
-        <v>46112</v>
+        <v>46128</v>
       </c>
       <c r="B75" t="s">
         <v>18</v>
@@ -7105,7 +7105,7 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="5">
-        <v>46112</v>
+        <v>46128</v>
       </c>
       <c r="B76" t="s">
         <v>19</v>
@@ -7119,7 +7119,7 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="5">
-        <v>46112</v>
+        <v>46128</v>
       </c>
       <c r="B77" t="s">
         <v>20</v>
@@ -7133,7 +7133,7 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="5">
-        <v>46112</v>
+        <v>46128</v>
       </c>
       <c r="B78" t="s">
         <v>21</v>
@@ -7147,7 +7147,7 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="5">
-        <v>46112</v>
+        <v>46128</v>
       </c>
       <c r="B79" t="s">
         <v>9</v>
@@ -7161,7 +7161,7 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="5">
-        <v>46112</v>
+        <v>46128</v>
       </c>
       <c r="B80" t="s">
         <v>15</v>
@@ -7175,7 +7175,7 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="5">
-        <v>46112</v>
+        <v>46128</v>
       </c>
       <c r="B81" t="s">
         <v>16</v>
@@ -7189,7 +7189,7 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="5">
-        <v>46112</v>
+        <v>46128</v>
       </c>
       <c r="B82" t="s">
         <v>17</v>
@@ -7203,7 +7203,7 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="5">
-        <v>46112</v>
+        <v>46128</v>
       </c>
       <c r="B83" t="s">
         <v>18</v>
@@ -7217,7 +7217,7 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="5">
-        <v>46112</v>
+        <v>46128</v>
       </c>
       <c r="B84" t="s">
         <v>19</v>
@@ -7231,7 +7231,7 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="5">
-        <v>46112</v>
+        <v>46128</v>
       </c>
       <c r="B85" t="s">
         <v>20</v>
@@ -7245,7 +7245,7 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="5">
-        <v>46112</v>
+        <v>46128</v>
       </c>
       <c r="B86" t="s">
         <v>21</v>
@@ -7259,7 +7259,7 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="5">
-        <v>46112</v>
+        <v>46128</v>
       </c>
       <c r="B87" t="s">
         <v>9</v>
@@ -7273,7 +7273,7 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="5">
-        <v>46112</v>
+        <v>46128</v>
       </c>
       <c r="B88" t="s">
         <v>15</v>
@@ -7287,7 +7287,7 @@
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="5">
-        <v>46112</v>
+        <v>46128</v>
       </c>
       <c r="B89" t="s">
         <v>16</v>
@@ -7301,7 +7301,7 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="5">
-        <v>46112</v>
+        <v>46128</v>
       </c>
       <c r="B90" t="s">
         <v>17</v>
@@ -7315,7 +7315,7 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="5">
-        <v>46112</v>
+        <v>46128</v>
       </c>
       <c r="B91" t="s">
         <v>18</v>
@@ -7329,7 +7329,7 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="5">
-        <v>46112</v>
+        <v>46128</v>
       </c>
       <c r="B92" t="s">
         <v>19</v>
@@ -7343,7 +7343,7 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="5">
-        <v>46112</v>
+        <v>46128</v>
       </c>
       <c r="B93" t="s">
         <v>20</v>
@@ -7357,7 +7357,7 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="5">
-        <v>46112</v>
+        <v>46128</v>
       </c>
       <c r="B94" t="s">
         <v>21</v>
@@ -7371,7 +7371,7 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="5">
-        <v>46112</v>
+        <v>46128</v>
       </c>
       <c r="B95" s="3" t="s">
         <v>22</v>
@@ -7385,7 +7385,7 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="5">
-        <v>46112</v>
+        <v>46128</v>
       </c>
       <c r="B96" s="3" t="s">
         <v>22</v>
@@ -7399,7 +7399,7 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="5">
-        <v>46112</v>
+        <v>46128</v>
       </c>
       <c r="B97" s="3" t="s">
         <v>22</v>
@@ -7413,7 +7413,7 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" s="5">
-        <v>46112</v>
+        <v>46128</v>
       </c>
       <c r="B98" s="3" t="s">
         <v>56</v>
@@ -7427,7 +7427,7 @@
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" s="5">
-        <v>46112</v>
+        <v>46128</v>
       </c>
       <c r="B99" s="3" t="s">
         <v>56</v>
@@ -7441,7 +7441,7 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="5">
-        <v>46112</v>
+        <v>46128</v>
       </c>
       <c r="B100" s="3" t="s">
         <v>56</v>
@@ -7455,7 +7455,7 @@
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="5">
-        <v>46112</v>
+        <v>46128</v>
       </c>
       <c r="B101" s="3" t="s">
         <v>60</v>
@@ -7469,7 +7469,7 @@
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="5">
-        <v>46112</v>
+        <v>46128</v>
       </c>
       <c r="B102" s="3" t="s">
         <v>60</v>
@@ -7483,7 +7483,7 @@
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" s="5">
-        <v>46112</v>
+        <v>46128</v>
       </c>
       <c r="B103" s="3" t="s">
         <v>60</v>
@@ -7497,7 +7497,7 @@
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="5">
-        <v>46112</v>
+        <v>46128</v>
       </c>
       <c r="B104" s="3" t="s">
         <v>68</v>
@@ -7511,7 +7511,7 @@
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" s="5">
-        <v>46112</v>
+        <v>46128</v>
       </c>
       <c r="B105" s="3" t="s">
         <v>68</v>
@@ -7525,7 +7525,7 @@
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="5">
-        <v>46112</v>
+        <v>46128</v>
       </c>
       <c r="B106" s="3" t="s">
         <v>68</v>
@@ -7539,7 +7539,7 @@
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="5">
-        <v>46112</v>
+        <v>46128</v>
       </c>
       <c r="B107" s="14" t="s">
         <v>72</v>
@@ -7553,7 +7553,7 @@
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" s="5">
-        <v>46112</v>
+        <v>46128</v>
       </c>
       <c r="B108" s="14" t="s">
         <v>72</v>
@@ -7567,7 +7567,7 @@
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" s="5">
-        <v>46112</v>
+        <v>46128</v>
       </c>
       <c r="B109" s="14" t="s">
         <v>72</v>
@@ -7581,7 +7581,7 @@
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" s="5">
-        <v>46113</v>
+        <v>46129</v>
       </c>
       <c r="B110" t="s">
         <v>9</v>
@@ -7595,7 +7595,7 @@
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" s="5">
-        <v>46113</v>
+        <v>46129</v>
       </c>
       <c r="B111" t="s">
         <v>15</v>
@@ -7609,7 +7609,7 @@
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" s="5">
-        <v>46113</v>
+        <v>46129</v>
       </c>
       <c r="B112" t="s">
         <v>16</v>
@@ -7623,7 +7623,7 @@
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" s="5">
-        <v>46113</v>
+        <v>46129</v>
       </c>
       <c r="B113" t="s">
         <v>17</v>
@@ -7637,7 +7637,7 @@
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" s="5">
-        <v>46113</v>
+        <v>46129</v>
       </c>
       <c r="B114" t="s">
         <v>18</v>
@@ -7651,7 +7651,7 @@
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="5">
-        <v>46113</v>
+        <v>46129</v>
       </c>
       <c r="B115" t="s">
         <v>19</v>
@@ -7665,7 +7665,7 @@
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="5">
-        <v>46113</v>
+        <v>46129</v>
       </c>
       <c r="B116" t="s">
         <v>20</v>
@@ -7679,7 +7679,7 @@
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" s="5">
-        <v>46113</v>
+        <v>46129</v>
       </c>
       <c r="B117" t="s">
         <v>21</v>
@@ -7693,7 +7693,7 @@
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" s="5">
-        <v>46113</v>
+        <v>46129</v>
       </c>
       <c r="B118" t="s">
         <v>9</v>
@@ -7707,7 +7707,7 @@
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" s="5">
-        <v>46113</v>
+        <v>46129</v>
       </c>
       <c r="B119" t="s">
         <v>15</v>
@@ -7721,7 +7721,7 @@
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" s="5">
-        <v>46113</v>
+        <v>46129</v>
       </c>
       <c r="B120" t="s">
         <v>16</v>
@@ -7735,7 +7735,7 @@
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" s="5">
-        <v>46113</v>
+        <v>46129</v>
       </c>
       <c r="B121" t="s">
         <v>17</v>
@@ -7749,7 +7749,7 @@
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" s="5">
-        <v>46113</v>
+        <v>46129</v>
       </c>
       <c r="B122" t="s">
         <v>18</v>
@@ -7763,7 +7763,7 @@
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" s="5">
-        <v>46113</v>
+        <v>46129</v>
       </c>
       <c r="B123" t="s">
         <v>19</v>
@@ -7777,7 +7777,7 @@
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" s="5">
-        <v>46113</v>
+        <v>46129</v>
       </c>
       <c r="B124" t="s">
         <v>20</v>
@@ -7791,7 +7791,7 @@
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" s="5">
-        <v>46113</v>
+        <v>46129</v>
       </c>
       <c r="B125" t="s">
         <v>21</v>
@@ -7805,7 +7805,7 @@
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" s="5">
-        <v>46113</v>
+        <v>46129</v>
       </c>
       <c r="B126" t="s">
         <v>9</v>
@@ -7819,7 +7819,7 @@
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" s="5">
-        <v>46113</v>
+        <v>46129</v>
       </c>
       <c r="B127" t="s">
         <v>15</v>
@@ -7833,7 +7833,7 @@
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" s="5">
-        <v>46113</v>
+        <v>46129</v>
       </c>
       <c r="B128" t="s">
         <v>16</v>
@@ -7847,7 +7847,7 @@
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" s="5">
-        <v>46113</v>
+        <v>46129</v>
       </c>
       <c r="B129" t="s">
         <v>17</v>
@@ -7861,7 +7861,7 @@
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" s="5">
-        <v>46113</v>
+        <v>46129</v>
       </c>
       <c r="B130" t="s">
         <v>18</v>
@@ -7875,7 +7875,7 @@
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" s="5">
-        <v>46113</v>
+        <v>46129</v>
       </c>
       <c r="B131" t="s">
         <v>19</v>
@@ -7889,7 +7889,7 @@
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" s="5">
-        <v>46113</v>
+        <v>46129</v>
       </c>
       <c r="B132" t="s">
         <v>20</v>
@@ -7903,7 +7903,7 @@
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" s="5">
-        <v>46113</v>
+        <v>46129</v>
       </c>
       <c r="B133" t="s">
         <v>21</v>
@@ -7917,7 +7917,7 @@
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" s="5">
-        <v>46113</v>
+        <v>46129</v>
       </c>
       <c r="B134" s="3" t="s">
         <v>22</v>
@@ -7931,7 +7931,7 @@
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" s="5">
-        <v>46113</v>
+        <v>46129</v>
       </c>
       <c r="B135" s="3" t="s">
         <v>22</v>
@@ -7945,7 +7945,7 @@
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" s="5">
-        <v>46113</v>
+        <v>46129</v>
       </c>
       <c r="B136" s="3" t="s">
         <v>22</v>
@@ -7959,7 +7959,7 @@
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" s="5">
-        <v>46113</v>
+        <v>46129</v>
       </c>
       <c r="B137" s="3" t="s">
         <v>56</v>
@@ -7973,7 +7973,7 @@
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" s="5">
-        <v>46113</v>
+        <v>46129</v>
       </c>
       <c r="B138" s="3" t="s">
         <v>56</v>
@@ -7987,7 +7987,7 @@
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" s="5">
-        <v>46113</v>
+        <v>46129</v>
       </c>
       <c r="B139" s="3" t="s">
         <v>56</v>
@@ -8001,7 +8001,7 @@
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" s="5">
-        <v>46113</v>
+        <v>46129</v>
       </c>
       <c r="B140" s="3" t="s">
         <v>60</v>
@@ -8015,7 +8015,7 @@
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" s="5">
-        <v>46113</v>
+        <v>46129</v>
       </c>
       <c r="B141" s="3" t="s">
         <v>60</v>
@@ -8029,7 +8029,7 @@
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" s="5">
-        <v>46113</v>
+        <v>46129</v>
       </c>
       <c r="B142" s="3" t="s">
         <v>60</v>
@@ -8043,7 +8043,7 @@
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" s="5">
-        <v>46113</v>
+        <v>46129</v>
       </c>
       <c r="B143" s="3" t="s">
         <v>68</v>
@@ -8057,7 +8057,7 @@
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" s="5">
-        <v>46113</v>
+        <v>46129</v>
       </c>
       <c r="B144" s="3" t="s">
         <v>68</v>
@@ -8071,7 +8071,7 @@
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" s="5">
-        <v>46113</v>
+        <v>46129</v>
       </c>
       <c r="B145" s="3" t="s">
         <v>68</v>
@@ -8085,7 +8085,7 @@
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" s="5">
-        <v>46113</v>
+        <v>46129</v>
       </c>
       <c r="B146" s="14" t="s">
         <v>72</v>
@@ -8099,7 +8099,7 @@
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" s="5">
-        <v>46113</v>
+        <v>46129</v>
       </c>
       <c r="B147" s="14" t="s">
         <v>72</v>
@@ -8113,7 +8113,7 @@
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" s="5">
-        <v>46113</v>
+        <v>46129</v>
       </c>
       <c r="B148" s="14" t="s">
         <v>72</v>
